--- a/data-raw/public-site/moa-machine-county/xlsx/case-year-2024-batch04.xlsx
+++ b/data-raw/public-site/moa-machine-county/xlsx/case-year-2024-batch04.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">隰县</t>
   </si>
   <si>
-    <t xml:space="preserve">玉露香梨</t>
+    <t xml:space="preserve">香梨</t>
   </si>
   <si>
     <t xml:space="preserve">山西稷山板枣机械化生产模式与典型案例</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">丘陵地区</t>
   </si>
   <si>
-    <t xml:space="preserve">鲜食葡萄</t>
+    <t xml:space="preserve">葡萄</t>
   </si>
   <si>
     <t xml:space="preserve">新疆南疆鲜食/制干葡萄机械化生产模式与典型案例</t>
@@ -158,9 +158,6 @@
     <t xml:space="preserve">南疆</t>
   </si>
   <si>
-    <t xml:space="preserve">鲜食/制干葡萄</t>
-  </si>
-  <si>
     <t xml:space="preserve">江苏连云港葡萄智能化生产模式与典型案例</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t xml:space="preserve">连云港</t>
   </si>
   <si>
-    <t xml:space="preserve">葡萄</t>
-  </si>
-  <si>
     <t xml:space="preserve">浙江兰溪丘陵山地杨梅机械化生产模式与典型案例</t>
   </si>
   <si>
@@ -197,10 +191,7 @@
     <t xml:space="preserve">安徽</t>
   </si>
   <si>
-    <t xml:space="preserve">黄山徽州</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄山毛峰</t>
+    <t xml:space="preserve">徽州</t>
   </si>
   <si>
     <t xml:space="preserve">浙江诸暨低山丘陵茶叶机械化生产模式和典型案例</t>
@@ -963,7 +954,7 @@
         <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
@@ -983,16 +974,16 @@
         <v>7</v>
       </c>
       <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" t="s">
         <v>49</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>50</v>
       </c>
-      <c r="H14" t="s">
-        <v>51</v>
-      </c>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -1012,16 +1003,16 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
         <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
@@ -1032,7 +1023,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -1041,16 +1032,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -1061,7 +1052,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -1070,16 +1061,16 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" t="s">
         <v>59</v>
       </c>
-      <c r="G17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" t="s">
-        <v>61</v>
-      </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
@@ -1090,7 +1081,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -1099,16 +1090,16 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
         <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -1119,7 +1110,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -1128,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" t="s">
         <v>66</v>
-      </c>
-      <c r="G19" t="s">
-        <v>67</v>
-      </c>
-      <c r="H19" t="s">
-        <v>68</v>
-      </c>
-      <c r="I19" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -1148,7 +1139,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -1157,16 +1148,16 @@
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
         <v>29</v>
       </c>
       <c r="H20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21">
@@ -1177,7 +1168,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
@@ -1186,16 +1177,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
@@ -1206,7 +1197,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
@@ -1215,14 +1206,14 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H22"/>
       <c r="I22" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
@@ -1233,7 +1224,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
@@ -1242,16 +1233,16 @@
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
@@ -1262,7 +1253,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D24" t="n">
         <v>23</v>
@@ -1271,14 +1262,14 @@
         <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H24"/>
       <c r="I24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
@@ -1289,7 +1280,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D25" t="n">
         <v>24</v>
@@ -1298,16 +1289,16 @@
         <v>7</v>
       </c>
       <c r="F25" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s">
         <v>83</v>
-      </c>
-      <c r="G25" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" t="s">
-        <v>85</v>
-      </c>
-      <c r="I25" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
